--- a/Aplicativos/pendencias/bd_saida/Loja 008.xlsx
+++ b/Aplicativos/pendencias/bd_saida/Loja 008.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,22 +461,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>21555</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AGUA MIN FLORESTA 500ML C GAS</t>
+          <t>PANO PANOSUL MEDIO ESTAMP 45X65 R23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15316</t>
+          <t>37467</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -488,35 +488,35 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>461</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>168</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2161</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ARROZ BCO ALEGRETE TP1 5KG</t>
+          <t>PANO PANOSUL MICROFIBRA 35X35CM SORTIDO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>33183</t>
+          <t>37467</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -524,35 +524,35 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>21557</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ARROZ BCO REQUINTE TP1 5KG</t>
+          <t>PANO PTO PANOSUL COLOR C EST</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>33831</t>
+          <t>37467</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -560,35 +560,35 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>525</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>8018</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BARRA CEREAL RITTER 25G BAN AVEIA MEL</t>
+          <t>SACO PANOSUL 60X68CM XADREZ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>35808</t>
+          <t>37467</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
@@ -605,22 +605,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13712</t>
+          <t>24968</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BOMBOM NESTLE ESPECIALIDADES 251G</t>
+          <t>TOAL ROSTO FAVO 40X60</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>33870</t>
+          <t>37467</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -632,35 +632,35 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>900</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4499</t>
+          <t>24984</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BUCHA VEGETAL VINI LADY 5003</t>
+          <t>TOAL SOCIAL PANOSUL 23X38CM</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>33737</t>
+          <t>37467</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -668,31 +668,31 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>119</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>25000</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CERV BRAHMA CHOPP LT 350ML ZERO</t>
+          <t>TOALHINHA KIDS 25X25CM</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>33737</t>
+          <t>37467</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -704,35 +704,35 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>313</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>37563</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CERVEJA ITAIPAVA LN 330ML MALZBIER</t>
+          <t>ABRIDOR LT E GFA INOX 9CM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>33737</t>
+          <t>39904</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -740,31 +740,31 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>182</v>
+        <v>72</v>
       </c>
       <c r="H9" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>33373</t>
+          <t>3885</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DESO AERO AXE 200ML BLACK ALE E CED</t>
+          <t>ABS C ABAS ALWAYS 16UN BASICA SUAVE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>33737</t>
+          <t>41455</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>107</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
@@ -785,26 +785,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9983</t>
+          <t>2925</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DESOD SANIT GOTA LIMPA 25G EUCALIPTO</t>
+          <t>ACHOC LIQ ITALAC 1L</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>33737</t>
+          <t>41455</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="H11" t="n">
         <v>2</v>
@@ -821,26 +821,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DET LIQ GOTA LIMPA 500ML CRISTAL</t>
+          <t>AGUA MIN AGUA DA PEDRA PET 5L S GAS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>33918</t>
+          <t>40320</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>21/03/2026</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -848,35 +848,35 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>51</v>
+        <v>544</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>3948</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ENERG MONSTER LT 473ML GREEN</t>
+          <t>AGUA SANIT GOTA LIMPA 1L</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>33918</t>
+          <t>39512</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -884,35 +884,35 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>306</v>
+        <v>418</v>
       </c>
       <c r="H13" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>12289</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ENERG MONSTER LT 473ML GREEN ZERO</t>
+          <t>AGUA SANIT IMPERIAL 1L</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>33918</t>
+          <t>41455</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -920,35 +920,35 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="H14" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>12291</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ENERG MONSTER LT 473ML MANGO LOCO</t>
+          <t>AGUA SANIT IMPERIAL 5L</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>33918</t>
+          <t>37648</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -956,35 +956,35 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>31</v>
+        <v>213</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ENERG MONSTER LT 473ML ULTRA</t>
+          <t>AGUA SANIT Q BOA 1L</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>33918</t>
+          <t>41455</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -992,35 +992,35 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>9539</t>
+          <t>8838</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FRALDA BABYSEC ULTRA JUMBINHO G 16UN</t>
+          <t>AMAC AQUAFAST 2L ROSA JARD FLORI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>32924</t>
+          <t>39512</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1028,31 +1028,31 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>15</v>
+        <v>173</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>18748</t>
+          <t>4147</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FRALDA DESC FERINHA JUMBINHO C/18 M</t>
+          <t>AMAC CONC COMFORT 400ML RF FRESCOR INTENS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>32924</t>
+          <t>41455</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1064,35 +1064,35 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3627</t>
+          <t>4157</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GELATINA NEILAR 20G PESSEGO</t>
+          <t>AMAC CONC COMFORT 900ML INT CUID E DOYP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>33918</t>
+          <t>37648</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1100,31 +1100,31 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>21298</t>
+          <t>4178</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ODORIZ AMAZONIA AROM 270ML BROTO</t>
+          <t>AMAC DOWNY 1 5L LIRIOS DO CAMPO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>33737</t>
+          <t>41455</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1136,35 +1136,35 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>1128</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>21306</t>
+          <t>12395</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ODORIZ AMAZONIA AROM 270ML SEMENTE</t>
+          <t>AMACIANTE AQUAFAST 2L VERM SED</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>33737</t>
+          <t>39512</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
@@ -1181,26 +1181,26 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>21661</t>
+          <t>12528</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PAPEL HIG DOBLE FD 4 UN C 30M</t>
+          <t>AP GILLETTE C 8 L8P6</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>35808</t>
+          <t>39512</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>204</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
@@ -1217,26 +1217,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>21663</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PAPEL HIG DOBLE FT FD 4 UN C 20M</t>
+          <t>AP PROBAK II LV7 PG5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>35808</t>
+          <t>40624</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
@@ -1253,22 +1253,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>33218</t>
+          <t>4264</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PAPEL HIG DOBLE SKIN FD 6 UN C 40M</t>
+          <t>AP VENUS SIMPLY LV4 PG3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>35808</t>
+          <t>40624</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1280,35 +1280,35 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>21694</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PAPEL HIG NESS FD 20M 12UN</t>
+          <t>ARROZ BCO OESTE TP1 2KG</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>35808</t>
+          <t>41455</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1316,35 +1316,35 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>21696</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PAPEL HIG NESS FD 4UN DE 30M</t>
+          <t>ARROZ BCO SABOROSO TP1 2KG</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>35808</t>
+          <t>41455</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
@@ -1361,26 +1361,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7366</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PAPEL HIG STYLUS 12 UN DE20M NEUTRO</t>
+          <t>ARROZ BCO SANO OURO TP1 2KG</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>35808</t>
+          <t>41455</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1388,35 +1388,35 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>21702</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PAPEL HIG SULINO NEUTRO FS FD 4UN DE 60M</t>
+          <t>ARROZ BCO SANO TP1 5KG</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>35808</t>
+          <t>41455</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1424,35 +1424,35 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>6</v>
+        <v>361</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7376</t>
+          <t>2242</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PAPEL TOALHA MAXIM STYLUS 2RL 50UN</t>
+          <t>ARROZ PARBO RAROZ TP1 5KG</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>35808</t>
+          <t>41455</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1460,35 +1460,35 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>15</v>
+        <v>141</v>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>2244</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PAPEL TOALHA MILI 2UN</t>
+          <t>ARROZ PARBO SABOROSO TP1 5KG</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>35808</t>
+          <t>41455</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>96</v>
+        <v>146</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
@@ -1505,26 +1505,26 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>21733</t>
+          <t>37190</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PAPEL TOALHA MILI BIANCO 2UN</t>
+          <t>AVENTAL POLIESTER 53X73</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>35808</t>
+          <t>39904</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1532,35 +1532,35 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>316</v>
+        <v>54</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>21734</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PAPEL TOALHA NATUREZA FD 2UN</t>
+          <t>BALA DORI GELATINA 13G AMORA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>35808</t>
+          <t>41939</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="H32" t="n">
         <v>2</v>
@@ -1577,26 +1577,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PIPOCA DOCE KEVYTOS 13G</t>
+          <t>BALA DORI GELATINA 13G BANANA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>33582</t>
+          <t>41939</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>07/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1604,35 +1604,35 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>311</v>
+        <v>45</v>
       </c>
       <c r="H33" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>33870</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>REFRE HAPPY TP 200ML MORANGO</t>
+          <t>BALA DORI GELATINA 13G BOCA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>33918</t>
+          <t>41939</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1640,35 +1640,35 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>33872</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>REFRE HAPPY TP 200ML PESSEGO</t>
+          <t>BALA DORI GELATINA 13G MINHOCA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>33918</t>
+          <t>41939</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1676,35 +1676,35 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="H35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>33868</t>
+          <t>12919</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>REFRE HAPPY TP 200ML UVA</t>
+          <t>BALAO LISO 6 5 C 30 AZUL</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>33918</t>
+          <t>39456</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1712,35 +1712,35 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>10</v>
+        <v>582</v>
       </c>
       <c r="H36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>12971</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>REFRE PO GLUP 15G ABACAXI</t>
+          <t>BALAO ZERINHO C 100 SORT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>33918</t>
+          <t>36953</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1748,71 +1748,71 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>334</v>
+        <v>293</v>
       </c>
       <c r="H37" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>37165</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>REFRE PO GLUP 15G LARANJA</t>
+          <t>BALEIRO DE VIDRO COM TAMPA 12X9 5CM</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>33918</t>
+          <t>39904</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
         <v>60</v>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>008</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>557</v>
-      </c>
       <c r="H38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>4499</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>REFRE PO GLUP 15G MARACUJA</t>
+          <t>BUCHA VEGETAL VINI LADY 5003</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>33918</t>
+          <t>38835</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1820,35 +1820,35 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1224</v>
+        <v>102</v>
       </c>
       <c r="H39" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>15090</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>REFRIG ANTARCTICA GUARANA LT 350ML</t>
+          <t>CAD ESPI CD 1X1 80FLS SWEETNESS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>33737</t>
+          <t>39456</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1856,35 +1856,35 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>299</v>
+        <v>108</v>
       </c>
       <c r="H40" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>15585</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>REFRIG FANTA LARANJA PET 600ML</t>
+          <t>CARGA GILLETTE MACH3 C 2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>33737</t>
+          <t>39512</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1892,35 +1892,35 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>358</v>
+        <v>3170</v>
       </c>
       <c r="H41" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>4567</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>REFRIG FRUKI PET 2L LARANJINHA</t>
+          <t>CARGA MACH 3 LV4 PG3 REGULAR</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>33737</t>
+          <t>40624</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1928,35 +1928,35 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="H42" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>154</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>REFRIG SARANDI PET 1 5L GUARANA ZERO</t>
+          <t>CERV BRAHMA DUPLO MALTE LT 473ML</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>33737</t>
+          <t>38255</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1964,35 +1964,35 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>60</v>
+        <v>314</v>
       </c>
       <c r="H43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>REFRIG SUKITA PET 2L LARANJA</t>
+          <t>CERV SKOL PILSEN LT 473ML</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>33737</t>
+          <t>39139</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2000,35 +2000,35 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>137</v>
+        <v>594</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>219</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>REFRIG SUKITA PET 2L UVA</t>
+          <t>CERV STELLA ARTOIS LT 473ML</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>33737</t>
+          <t>38255</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2036,35 +2036,35 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>135</v>
+        <v>318</v>
       </c>
       <c r="H45" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>8018</t>
+          <t>159</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SACO PANOSUL 60X68CM XADREZ</t>
+          <t>CERVEJA CORONA LT 473ML EXTRA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>35808</t>
+          <t>41455</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2072,35 +2072,35 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>3</v>
+        <v>221</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>24323</t>
+          <t>178</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SH GENIAL PET 2 EM 1 500ML</t>
+          <t>CERVEJA KAISER LT 473ML</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>35808</t>
+          <t>41200</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2108,35 +2108,35 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>24</v>
+        <v>872</v>
       </c>
       <c r="H47" t="n">
-        <v>5</v>
+        <v>110</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>8236</t>
+          <t>295</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SH HEAD &amp; SHOULDERS 400ML ANTI COCEIRA</t>
+          <t>CERVEJA STELLA ARTOIS LN 330ML PURE GOLD</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>33737</t>
+          <t>41455</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H48" t="n">
         <v>1</v>
@@ -2153,26 +2153,26 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8274</t>
+          <t>142</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SHAMPOO PALMOLIVE 350ML NUTRICAO EXTRA</t>
+          <t>CERVEJA STELLA ONE W 600ML</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>32924</t>
+          <t>41455</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2180,46 +2180,5662 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>34754</t>
+          <t>1743</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SUCO DE UVA TREBOM VD 1 5L</t>
+          <t>CHICLE FREEGELLS GUM 8G CANELA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>33918</t>
+          <t>41939</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E50" t="n">
+        <v>15</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>23</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1746</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CHICLE FREEGELLS GUM 8G MELANCIA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>41939</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>15</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>12</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1745</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CHICLE FREEGELLS GUM 8G MENTA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>41939</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>15</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>7</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1740</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CHICLE FREEGELLS GUM 8G MORANGO</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>41939</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>15</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>616</v>
+      </c>
+      <c r="H53" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1744</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CHICLE FREEGELLS GUM 8G TUTTI FRUTTI</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>41939</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>15</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>19</v>
+      </c>
+      <c r="H54" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>37166</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>COLA ADESIVA PEGA RATO</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>39904</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>60</v>
+      </c>
+      <c r="H55" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>COLHER MESA TRAM INOX LEME PRETA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>40519</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>21/03/2026</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>60</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>23</v>
+      </c>
+      <c r="H56" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>16443</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>COMEDOURO PET MELAMINA DUPLO 1 2L</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>39904</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>165</v>
+      </c>
+      <c r="H57" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>37145</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>COMEDOURO PET PLASTICO 5 5X15</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>39904</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>108</v>
+      </c>
+      <c r="H58" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>37152</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>COMEDOURO PET PLASTICO 6 5X20 5</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>39904</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>54</v>
+      </c>
+      <c r="H59" t="n">
         <v>6</v>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>008</t>
-        </is>
-      </c>
-      <c r="G50" t="n">
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>15640</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>COND DARLING 350ML DETOX</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>37648</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>5003</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>COND PALMOLIVE 350ML CERAMIDAS FORCE</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>37648</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>2</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>5011</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>COND PALMOLIVE 350ML NEUTRO</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>37648</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>5030</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>COND PANTENE 175ML LISO EXTREMO</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>40624</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>12</v>
+      </c>
+      <c r="H63" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>37309</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>COPO VIDRO C BORDA DOURADA 40ML</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>39904</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>16</v>
+      </c>
+      <c r="H64" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>37180</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CORDA P VARAL POLIESTER C 3 4MMX5M</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>39904</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>72</v>
+      </c>
+      <c r="H65" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>37186</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>CORTINA P BOX EVA 0 6M 180X180</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>39904</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>24</v>
+      </c>
+      <c r="H66" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>19312</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>COT HASTES FLEX COTTONBABY C 75</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>37648</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>72</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>6</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>16656</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>CP C CAN PLAST COLORS 4UN</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>39904</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>84</v>
+      </c>
+      <c r="H68" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>16807</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>CP VIDRO SHOT CAVEIRA 50ML</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>39904</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>12</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>8</v>
+      </c>
+      <c r="H69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>16808</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>CP VIDRO SODA LIME 320ML</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>39456</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>83</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>5220</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>CR DEN COLGATE 90G MPA</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>41455</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>72</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>144</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>5217</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>CR DEN COLGATE 90G NAT EXT CARVAO</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>37648</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>48</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>108</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>16830</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CR DENT COLGATE MPA 120G</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>37648</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>72</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>82</v>
+      </c>
+      <c r="H73" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>5226</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>CR DENT COLGATE T ACAO 90G ORIG</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>37648</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>72</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>185</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5247</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>CR DENT SORRISO 90G DENTES BCOS</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>37648</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>12</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>22</v>
+      </c>
+      <c r="H75" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>5276</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>CR DENTAL TANDY 50G TUTTI FRUTI</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>37648</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>12</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>8</v>
+      </c>
+      <c r="H76" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>5277</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>CR DENTAL TANDY 50G UVA</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>37648</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>12</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>6</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>9280</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>DESINF AQUAFAST 1L PAIXAO</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>41455</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>12</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>6</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>17173</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>DESINF GOTA LIMPA 2L FLORAL</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>37648</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>203</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>17183</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>DESINF GOTA LIMPA 500ML PINHO</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>37648</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>12</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>83</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>17190</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>DESINF IMPERIAL 5L LAVANDA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>40210</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>21/03/2026</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>4</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>117</v>
+      </c>
+      <c r="H81" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>33374</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>DESO AERO AXE 200ML APO VET E MANDA</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>37648</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>12</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>21</v>
+      </c>
+      <c r="H82" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>5510</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>DESOD AERO AXE 152ML 90G MUSK</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>37648</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>12</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>2</v>
+      </c>
+      <c r="H83" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>17290</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>DESOD ROLLON DOVE 50ML</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>37648</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>12</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>5</v>
+      </c>
+      <c r="H84" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>17309</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>DESOD ROLLON REXONA 50ML F POWDER</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>40210</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>21/03/2026</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>12</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>18</v>
+      </c>
+      <c r="H85" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>17311</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>DESOD ROLLON REXONA 50ML INVISIBLE</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>37648</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>12</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>9</v>
+      </c>
+      <c r="H86" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>17324</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>DET LIQ AQUAFAST 1L MULTIACAO</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>37648</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>12</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>35698</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>DET LIQ BARBAREX 5L NEUTRO</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>37648</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>2</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>68</v>
+      </c>
+      <c r="H88" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>17388</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>DET PO APYCE SH 4K AZUL</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>41455</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>5</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>129</v>
+      </c>
+      <c r="H89" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>33423</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>DET PO AQUAFAST FLORES BAUNILH 800G</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>41455</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>20</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>35</v>
+      </c>
+      <c r="H90" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>17409</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>DET PO GIRANDO SOL ROSA SH 400G</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>37648</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>30</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>25</v>
+      </c>
+      <c r="H91" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1894</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>DROPS FREEGELLS 27 6G CEREJA CHOC</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>41939</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>12</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>1053</v>
+      </c>
+      <c r="H92" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>1843</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>DROPS FREEGELLS 27 9G CEREJA</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>41939</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>12</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>12</v>
+      </c>
+      <c r="H93" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>1850</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>DROPS FREEGELLS 27 9G FRESH MELAO</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>41939</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>12</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>67</v>
+      </c>
+      <c r="H94" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1852</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>DROPS FREEGELLS 27 9G MENTA</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>41939</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>12</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>15</v>
+      </c>
+      <c r="H95" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>1847</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>DROPS FREEGELLS 27 9G VIT C CITRUS</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>41939</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>12</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>21</v>
+      </c>
+      <c r="H96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>17473</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>DUCHA ELETR ADVANCED 220V 7500W</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>40442</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>21/03/2026</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
         <v>10</v>
       </c>
-      <c r="H50" t="n">
+      <c r="H97" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>35021</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>DUCHA SS ZAGONEL 3T 220V BCA</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>40442</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>21/03/2026</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>12</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>106</v>
+      </c>
+      <c r="H98" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>526</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ENERG RED BULL LT 250ML TROPICAL</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>41455</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>24</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>9</v>
+      </c>
+      <c r="H99" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>5850</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>ESC DENTAL ORAL B PRO</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>40624</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>72</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>8</v>
+      </c>
+      <c r="H100" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>5848</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ESC DENTAL ORAL-B KIDS MICKEY</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>40624</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>36</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>6</v>
+      </c>
+      <c r="H101" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>33759</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>ESCOVA P MAMADEIRA CABO PLASTICO</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>39904</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>74</v>
+      </c>
+      <c r="H102" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>37157</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>ESPONJA P BANHO PLASTICO 50GR</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>39904</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>156</v>
+      </c>
+      <c r="H103" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>37160</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>ESPONJA P MAQUIAGEM C 7PCS</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>39904</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>84</v>
+      </c>
+      <c r="H104" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>37308</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>ESPREMEDOR LIMAO PLASTICO 21CM</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>39904</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>60</v>
+      </c>
+      <c r="H105" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>18429</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>FAR PANKO SANTI ORIENTAL 200G</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>37648</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>14</v>
+      </c>
+      <c r="H106" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>36987</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>FARINHA MANDIOCA 500G DINDA</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>41455</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>20</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>50</v>
+      </c>
+      <c r="H107" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>36992</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>FARINHA MANDIOCA DINDA 1KG EXTRA FINA</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>41455</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>10</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>29</v>
+      </c>
+      <c r="H108" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2677</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>FARINHA MANDIOCA YOKI 500G</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>41455</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>24</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>7</v>
+      </c>
+      <c r="H109" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2685</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>FARINHA MILHO SINHA 1KG MEDIA</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>37648</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>10</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>7</v>
+      </c>
+      <c r="H110" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>37074</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>FARINHA TAPIOCA ROCHA 400G BATATA</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>41455</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>10</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>40</v>
+      </c>
+      <c r="H111" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>37007</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>FAROFA DINDA 200G BACON</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>41455</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>25</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>7</v>
+      </c>
+      <c r="H112" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>37014</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>FAROFA DINDA 200G PICANHA</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>41455</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>25</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>27</v>
+      </c>
+      <c r="H113" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2771</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>FAROFA MANDIOCA PINDUCA 250G CHURRASCO</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>41455</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>12</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>17</v>
+      </c>
+      <c r="H114" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>37033</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>FAROFA ROCHA 400G TRAD</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>41455</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>10</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>47</v>
+      </c>
+      <c r="H115" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>37025</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>FAROFA ROCHA CASEIRA 300G CEB NA MANT</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>41455</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>10</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>5</v>
+      </c>
+      <c r="H116" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>FEIJAO CARIOCA SERRA URUGUAI 1KG</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>41455</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>30</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>28</v>
+      </c>
+      <c r="H117" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>9539</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>FRALDA BABYSEC ULTRA JUMBINHO G 16UN</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>38255</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>8</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>14</v>
+      </c>
+      <c r="H118" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>18745</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>FRALDA DESC FERINHA JUMBINHO C 14 GG</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>39512</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>12</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>30</v>
+      </c>
+      <c r="H119" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>18747</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>FRALDA DESC FERINHA JUMBINHO C/16 G</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>39512</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>12</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>31</v>
+      </c>
+      <c r="H120" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>6131</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>FRALDA DESC LOOMPIG JUMBINHO M 16 UN</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>39512</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>8</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>4</v>
+      </c>
+      <c r="H121" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>18762</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>FRALDA DESC MILI GIGA G C 78 C 78 G</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>38835</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>19/03/2026</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>4</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>6</v>
+      </c>
+      <c r="H122" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>18761</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>FRALDA DESC MILI GIGA XG C 68 C 68 XG</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>40210</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>21/03/2026</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>4</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>28</v>
+      </c>
+      <c r="H123" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>9550</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>FRALDA MILI JUMBINHO XXG 16UN</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>38835</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>19/03/2026</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>9</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>63</v>
+      </c>
+      <c r="H124" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>37312</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>GALHETEIRO VIDRO 150ML</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>39904</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>1</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>96</v>
+      </c>
+      <c r="H125" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>37311</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>GALHETEIRO VIDRO 250ML</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>39904</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>1</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>48</v>
+      </c>
+      <c r="H126" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>33754</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>GANCHO PLASTICO C3</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>39904</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>1</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>108</v>
+      </c>
+      <c r="H127" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>33753</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>GANCHO PLASTICO C4</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>39904</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>96</v>
+      </c>
+      <c r="H128" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>9594</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>GIRASSOL CBS 250G</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>37001</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>12</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>6</v>
+      </c>
+      <c r="H129" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>19340</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>INCENSO FLUTE C 8 CHAMANDO DINHE</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>40519</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>21/03/2026</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>25</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>36</v>
+      </c>
+      <c r="H130" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>19355</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>INCENSO FLUTE C 8 ROSA VERM</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>40519</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>21/03/2026</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>25</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>26</v>
+      </c>
+      <c r="H131" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>19359</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>INCENSO FLUTE C 8 TRES EM UM</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>40519</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>21/03/2026</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>25</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>7</v>
+      </c>
+      <c r="H132" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>19360</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>INCENSO FLUTE C 8 VERBENA</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>40519</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>21/03/2026</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>25</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>27</v>
+      </c>
+      <c r="H133" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>19378</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>INSET PROINSET SUPER ECONOMICO 750ML</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>41455</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>12</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>450</v>
+      </c>
+      <c r="H134" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>37154</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>JARRA VIDRO 1L</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>39904</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>1</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>60</v>
+      </c>
+      <c r="H135" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>19845</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>L MOVEIS POLWAX 200ML LAVANDA</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>37648</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>24</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>208</v>
+      </c>
+      <c r="H136" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>6631</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>LAMP ELGIN BULBO 9W 6500K 220V</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>40442</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>21/03/2026</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>10</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>631</v>
+      </c>
+      <c r="H137" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>19907</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>LAMP TRAM TP BULBO LED 9W 6500K</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>40442</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>21/03/2026</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>10</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>961</v>
+      </c>
+      <c r="H138" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>9735</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>LAVA ROUPA AQUA FAST 3L TERNURA</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>41455</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>4</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>11</v>
+      </c>
+      <c r="H139" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>6684</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>LAVA ROUPA AQUAFAST 5L MULTIACAO</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>39512</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>4</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>44</v>
+      </c>
+      <c r="H140" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>6692</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>LAVA ROUPA BRILHANTE 3L LIMPEZA TOTAL</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>37648</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>4</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>376</v>
+      </c>
+      <c r="H141" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>20064</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>LENC CASAL CORTTEX 200F MICROTEC</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>40307</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>21/03/2026</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>1</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>138</v>
+      </c>
+      <c r="H142" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>36733</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>LIMP PERF AQUAFAST 2L SEDUCAO</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>37648</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>6</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>32</v>
+      </c>
+      <c r="H143" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>6939</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>LIMP VIDRO AQUAFAST 500ML</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>37648</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>12</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>1</v>
+      </c>
+      <c r="H144" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>20193</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>LIXA P PES DUPLA FACE</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>39904</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>1</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>96</v>
+      </c>
+      <c r="H145" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2401</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>MILHO PIPOCA BELLA DICA 400GR</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>41455</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>12</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>250</v>
+      </c>
+      <c r="H146" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>MILHO PIPOCA SERRA URUGUAI TP1 400G</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>41455</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>20</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>174</v>
+      </c>
+      <c r="H147" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>21379</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>OLEO IPIRANGA F1 MASTER PERF 15W40 1L</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>40343</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>21/03/2026</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>24</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>32</v>
+      </c>
+      <c r="H148" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>21380</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>OLEO IPIRANGA MOTO PROT 20W50 SL</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>37001</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>24</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>22</v>
+      </c>
+      <c r="H149" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>7256</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>PALITO DENTAL GABOARDI 80UN PREMIUM</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>40519</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>21/03/2026</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>25</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>72</v>
+      </c>
+      <c r="H150" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>21674</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>PAPEL HIG FOFOLETTE FS 30M C 12</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>37001</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>6</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>66</v>
+      </c>
+      <c r="H151" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>21687</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>PAPEL HIG MILI PERFUM FLA DPL 30M 12UN</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>37001</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>8</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>147</v>
+      </c>
+      <c r="H152" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>21693</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>PAPEL HIG NATUPEL PREM FS 60M C 4</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>37001</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>16</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>150</v>
+      </c>
+      <c r="H153" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>21698</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>PAPEL HIG STYLUS FD 24 UN DE 20M NEUTRO</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>38835</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>19/03/2026</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>4</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>46</v>
+      </c>
+      <c r="H154" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>21733</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>PAPEL TOALHA MILI BIANCO 2UN</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>37001</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>12</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>416</v>
+      </c>
+      <c r="H155" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>1856</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>PAST DOCILE MINTY 14G LAR</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>41939</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>12</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>97</v>
+      </c>
+      <c r="H156" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>1854</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>PAST DOCILE MINTY 14G MOR</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>41939</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>12</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>50</v>
+      </c>
+      <c r="H157" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>1857</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>PAST DOCILE MINTY 14G TUTTI FRUTTI</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>41939</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>12</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>92</v>
+      </c>
+      <c r="H158" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>1837</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>PAST DOCILE ROLLY MINTY 29G FRUIT</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>41939</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>360</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>15</v>
+      </c>
+      <c r="H159" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>1838</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>PAST DOCILE ROLLY MINTY 29G HORTELA</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>41939</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>360</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>5</v>
+      </c>
+      <c r="H160" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>1839</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>PAST DOCILE ROLLY MINTY 29G MORANGO</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>41939</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>360</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>5</v>
+      </c>
+      <c r="H161" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>7423</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>PEDRA SANITARIA SANI-SOL 20G EUCALIPTO</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>41455</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>144</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>19</v>
+      </c>
+      <c r="H162" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>21856</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>PEN M BONI TARTARUGA R.0021B</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>39512</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>1</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>3</v>
+      </c>
+      <c r="H163" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>22124</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>POMADA WASSINGTON PASTA 36G MARROM</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>39512</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>12</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>1</v>
+      </c>
+      <c r="H164" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>22125</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>POMADA WASSINGTON PASTA 36G PTO</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>39512</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>12</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>7</v>
+      </c>
+      <c r="H165" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>37161</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>POTE HERMETICO C TAMPA BAMBU 200ML</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>39904</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>1</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>70</v>
+      </c>
+      <c r="H166" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>37310</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>RALADOR INOX 24 5CM</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>39904</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>1</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>180</v>
+      </c>
+      <c r="H167" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>37142</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>RALADOR METAL C CABO PLASTICO 20X10</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>39904</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>1</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>72</v>
+      </c>
+      <c r="H168" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>REFRE PO GLUP 15G MORANGO</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>41455</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>60</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>4</v>
+      </c>
+      <c r="H169" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>886</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>REFRIG ANTARCTICA GUAR LT 350ML ZR</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>41455</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>12</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>31</v>
+      </c>
+      <c r="H170" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>911</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>REFRIG ANTARCTICA GUARANA PET 200ML ZERO</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>41455</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>12</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
+        <v>156</v>
+      </c>
+      <c r="H171" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>REFRIG COCA COLA PET 200ML ZERO</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>41200</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>12</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
+        <v>227</v>
+      </c>
+      <c r="H172" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>REFRIG FRUKI PET 600ML LIMAO</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>41455</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>12</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G173" t="n">
+        <v>13</v>
+      </c>
+      <c r="H173" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>REFRIG PEPSI PET 3L</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>38255</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>4</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G174" t="n">
+        <v>116</v>
+      </c>
+      <c r="H174" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>909</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>REFRIG SPRITE LT 350ML</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>41200</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>6</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G175" t="n">
+        <v>175</v>
+      </c>
+      <c r="H175" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>22914</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>REPARADOR PONTAS JAYLUC 30ML BLIND QUERAT</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>39512</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>24</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G176" t="n">
+        <v>15</v>
+      </c>
+      <c r="H176" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>22915</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>REPARADOR PONTAS JAYLUC 30ML CERAMIDAS</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>39512</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>24</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G177" t="n">
+        <v>17</v>
+      </c>
+      <c r="H177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>22916</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>REPARADOR PONTAS JAYLUC 30ML OLEO ARGAN</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>39512</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>24</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>16</v>
+      </c>
+      <c r="H178" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>32162</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>SAB ALMA 130G FLORES JASMIN</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>39139</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>19/03/2026</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>48</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G179" t="n">
+        <v>3</v>
+      </c>
+      <c r="H179" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>34976</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>SAB MARAN SUAVE 80G ERVA DOCE</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>41455</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>108</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G180" t="n">
+        <v>61</v>
+      </c>
+      <c r="H180" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>23159</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>SABAO ZAVASKI GLIC 200G</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>41455</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>50</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G181" t="n">
+        <v>35</v>
+      </c>
+      <c r="H181" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>7951</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>SABON PALMOLIVE NATURALS 150G VERDE</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>37648</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>72</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G182" t="n">
+        <v>18</v>
+      </c>
+      <c r="H182" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>7968</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>SABONETE PROTEX 85G AVEIA</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>37648</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>72</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G183" t="n">
+        <v>6</v>
+      </c>
+      <c r="H183" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>24062</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>SAPONACEO CREM FONT 250ML CLORO</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>37648</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>12</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G184" t="n">
+        <v>2</v>
+      </c>
+      <c r="H184" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>24084</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>SC LIXO ALMOF CASAFORT 100L C 5</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>37001</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>50</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G185" t="n">
+        <v>12</v>
+      </c>
+      <c r="H185" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>24087</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>SC LIXO ALMOF CASAFORT 50L C 10</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>37001</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>50</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G186" t="n">
+        <v>5</v>
+      </c>
+      <c r="H186" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>24097</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>SC LIXO PRO LIXO ROLAO 150L C 10</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>37001</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>12</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G187" t="n">
+        <v>7</v>
+      </c>
+      <c r="H187" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>24102</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>SC LIXO PRO LIXO ROLINHO 100L C 5</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>37001</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>25</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G188" t="n">
+        <v>20</v>
+      </c>
+      <c r="H188" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>24105</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>SC LIXO PRO LIXO ROLINHO 50L C 10</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>37001</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>25</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G189" t="n">
+        <v>11</v>
+      </c>
+      <c r="H189" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>24107</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>SC LIXO ROL CASAFORT 100L C 10 AZ</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>37001</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>25</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G190" t="n">
+        <v>43</v>
+      </c>
+      <c r="H190" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>24113</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>SC LIXO ROL CASAFORT 15L C 40 AZ</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>37001</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>25</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G191" t="n">
+        <v>18</v>
+      </c>
+      <c r="H191" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>24115</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>SC LIXO ROL CASAFORT 30L C 20 PT</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>37001</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>25</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G192" t="n">
+        <v>31</v>
+      </c>
+      <c r="H192" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>24118</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>SC LIXO ROL CASAFORT 50L C 20 PT</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>37001</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>25</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G193" t="n">
+        <v>22</v>
+      </c>
+      <c r="H193" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>24126</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>SC LIXO ROL DOBRASIL 50L C 20 AZ</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>37001</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>25</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G194" t="n">
+        <v>9</v>
+      </c>
+      <c r="H194" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>24143</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>SC PLAST A VAC 60X80CM</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>39904</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>1</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G195" t="n">
+        <v>84</v>
+      </c>
+      <c r="H195" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>24323</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>SH GENIAL PET 2 EM 1 500ML</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>41455</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>1</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G196" t="n">
+        <v>24</v>
+      </c>
+      <c r="H196" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>8232</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>SH HEAD SHOULDERS 200ML PREV QUEDA</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>40624</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>6</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G197" t="n">
+        <v>8</v>
+      </c>
+      <c r="H197" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>10283</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>SH MONANGE 325ML REST Q GOSTO</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>37648</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>1</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G198" t="n">
+        <v>80</v>
+      </c>
+      <c r="H198" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>8296</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>SH PANTENE 200ML BAMBU</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>40624</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>6</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G199" t="n">
+        <v>16</v>
+      </c>
+      <c r="H199" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>8276</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>SHAMPOO PALMOLIVE 350ML NEUTRO</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>37648</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>6</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G200" t="n">
+        <v>2</v>
+      </c>
+      <c r="H200" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>SUCO DEL VALLE FRUT PET 1 5L FRUT CITRICAS</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>41200</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>6</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G201" t="n">
+        <v>106</v>
+      </c>
+      <c r="H201" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>SUCO DEL VALLE TP 200ML PESSEGO</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>41455</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>18</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G202" t="n">
+        <v>26</v>
+      </c>
+      <c r="H202" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>SUCO KAPO 200ML MACA</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>41200</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>12</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G203" t="n">
+        <v>164</v>
+      </c>
+      <c r="H203" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>34951</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>SUCO KAPO 200ML MELANCIA</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>41200</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>12</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G204" t="n">
+        <v>117</v>
+      </c>
+      <c r="H204" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>SUCO KAPO 200ML MORANGO</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>41200</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>12</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G205" t="n">
+        <v>196</v>
+      </c>
+      <c r="H205" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>37176</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>TAMPA SILICONE 190 160 140 115 90</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>39904</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>1</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G206" t="n">
+        <v>60</v>
+      </c>
+      <c r="H206" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
